--- a/daily_matches/job_matches_2026-05-04.xlsx
+++ b/daily_matches/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Growth Protocol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, Snowflake, BigQuery, Tableau, Power BI, Python</t>
+          <t>Data Scientist, RAG, MLflow, FastAPI, Docker, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22eed84f3a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, Snowflake, BigQuery, Tableau, Power BI, Python</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,112 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Thousand Oaks, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, AKS, Git, Databricks, Tableau, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d365d77aac9d7c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Intern Data Scientist</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee328749120b1dc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Thousand Oaks, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, AKS, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bac0c2dec6fe3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=69c818141f7c2040</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-04.xlsx
+++ b/daily_matches/job_matches_2026-05-04.xlsx
@@ -468,70 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Back-End Software Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Growth Protocol</t>
+          <t>Oak Ridge National Laboratory</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, FastAPI, Docker, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c9a1441fd4ec20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Senior Product Associate - CARD DATA OWNERS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, S3, Data Lake, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c818141f7c2040</t>
+          <t>https://www.indeed.com/viewjob?jk=a8d135304ef368d9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-04.xlsx
+++ b/daily_matches/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,875 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Back-End Software Developer</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oak Ridge National Laboratory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL</t>
+          <t>Redshift, BigQuery, Apache Airflow, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c9a1441fd4ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=e1612776e805e54c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Product Associate - CARD DATA OWNERS</t>
+          <t>Cloud Support Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Agivant Technologies</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sherman Oaks, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Matplotlib, Seaborn</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b088c9082407ec84</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DevOps Architect</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BigQuery, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e44cf21cb97515cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cloud Support Associate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Junior Cloud Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, Mistral, Pinecone, Prompt Engineering, Cortex, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72607660bad0675a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rebel</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, FastAPI, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Polars</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Cloud Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>S3, Glue, Athena, Data Lake, Snowflake, Tableau, Power BI, Quicksight, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a30ab82b34b6466</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>S3, Glue, Athena, Data Lake, Snowflake, Tableau, Power BI, Quicksight, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ddf6f51fef293c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7d56ecc6fc275b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Cluster Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Voleon Group</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Berkeley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>12.2</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, Data Lake, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8d135304ef368d9</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, S3, MLflow, Docker, Kubernetes, Terraform, Dask, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68a45157511d01d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Scientist II - Reservations</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22830778fbb9fbd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Snowflake, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6b490e9093e1fb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer, DevOps</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Voleon Group</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39ee11ff37277c6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Linux Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Voleon Group</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1df0dc0d6ff95795</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Pinecone, S3, Glue, Docker, Kubernetes, CI/CD, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca46fd03c73ce22e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Equus Computer Systems</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer – AI &amp; Industrial Applications</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Daimler Truck North America</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cleveland, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Docker, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f203c7802bc3193</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineering / Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BSI Financial Services</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ClinDCast LLC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Warren, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1769c749d29778e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6502a676b677e356</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=289ddda237a35ed8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Research Scientist 5G NR and 6G</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1489cd8bfd124930</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-04.xlsx
+++ b/daily_matches/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Photon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Shelby, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Apache Airflow, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PySpark</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1612776e805e54c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Support Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agivant Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sherman Oaks, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Matplotlib, Seaborn</t>
+          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b088c9082407ec84</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Strong Middle Data Scientist (Part-time)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mobilunity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BigQuery, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, Kafka, MySQL</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e44cf21cb97515cf</t>
+          <t>https://www.indeed.com/viewjob?jk=670a4f82148bab8c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, Gemini, Mistral, Pinecone, Prompt Engineering, Cortex, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
+          <t>https://www.indeed.com/viewjob?jk=812b6e434aab8990</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Mistral, Pinecone, Prompt Engineering, Cortex, CI/CD, GitHub Actions, Terraform</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72607660bad0675a</t>
+          <t>https://www.indeed.com/viewjob?jk=32d18419724cd3ba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr. Engineer, Software</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, FastAPI, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Polars</t>
+          <t>Prompt Engineering, Docker, Kubernetes, AKS, Jenkins, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2f794524fd07d4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Data Lake, Snowflake, Tableau, Power BI, Quicksight, Python, SQL</t>
+          <t>S3, EC2, Kinesis, CI/CD, Jenkins, Git, Kafka, PostgreSQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e54c3f102344248</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Agentic-Workflow MLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prophecy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, R</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, PyTorch, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a30ab82b34b6466</t>
+          <t>https://www.indeed.com/viewjob?jk=f77d1b6e188a130b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Agentic-Workflow MLE (Pipeline)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prophecy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Data Lake, Snowflake, Tableau, Power BI, Quicksight, Python, SQL</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, PyTorch, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
+          <t>https://www.indeed.com/viewjob?jk=846aaea452c65fef</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, R</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ddf6f51fef293c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, Python</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d56ecc6fc275b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f095b443e497d6af</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cluster Site Reliability Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, MLflow, Docker, Kubernetes, Terraform, Dask, Python</t>
+          <t>S3, Glue, Athena, Data Lake, Snowflake, Tableau, Power BI, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a45157511d01d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Scientist II - Reservations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Redshift, Data Lake, Kinesis, Git, Snowflake, Databricks, Redshift, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22830778fbb9fbd5</t>
+          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Integration Analyst</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b490e9093e1fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=1771d08147d48b57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer, DevOps</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ee11ff37277c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc636c225a3b0d08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Linux Infrastructure Engineer</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df0dc0d6ff95795</t>
+          <t>https://www.indeed.com/viewjob?jk=a50fc1fd9ca90a3e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Pinecone, S3, Glue, Docker, Kubernetes, CI/CD, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca46fd03c73ce22e</t>
+          <t>https://www.indeed.com/viewjob?jk=96b8ed1d172d9b21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d04c5be30ba114</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer – AI &amp; Industrial Applications</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Daimler Truck North America</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Docker, Git, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f203c7802bc3193</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a671ccb2726283</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=2f221630efd504e3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ClinDCast LLC</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1769c749d29778e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc2d513a8e5b667</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6502a676b677e356</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f25f1e33197c2f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,2422 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289ddda237a35ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c6ae4864018e645</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Research Scientist 5G NR and 6G</t>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=745c91a67f5c0012</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c77a8b7e9ecd77b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d7adac687752794</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cba193ac6d97ccbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7507f69c19e474b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a649dc00d49772be</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b7c533aa9e21c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80e409a84823432c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a233fead74765805</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79d47a75d49031cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ddaf778d2ea07d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3211deb36c26aaa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81e0393507a109a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9850b5f75c020c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d37ff9d3778876f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe6846c5c54476b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97ed7174a6ea4bd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9785a20aecf8c4de</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f134df25935ad9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32ace5e9fcbc7f44</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59568162ab93d7d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10a4b86bc11b9674</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524aa93a3570e54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d665d4a1825fc4fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9773846c6c6ee8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca1cf78f3eb8423c</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3924b6e60e9d7c59</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Culver City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f461788fecb2b2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46111a2e5b3eb086</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31390c647cdb4e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a05edd7bd552cee</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2705dc7ab469fca5</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=646a2aafce7cad2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Technical Commerce &amp; AI Consultant | Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9cb337dbc254290</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9ab2c35e170c6bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a0b2da90611b7f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Okta IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12437ed8f934c208</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AWS API Gateway Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AWS Technical Apprentice / Trainee</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, CI/CD, Jenkins, Terraform, Git, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=feb3059078a0901f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Capture</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pindrop</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D66" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40faec2ccdd7f2df</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Capture</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pindrop</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cef5340a7e060723</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f88bce0a152f0cfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ace6137fa8decf52</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd4b7cc82ae2d8aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aeec6a5322ee7f9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cde9cc897292db86</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8057aa6b94b62cf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, FastAPI, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6144f7e9ae450f13</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Hiring: NLP Architect – Generative AI &amp; Conversational Intelligence | 15+ Years of Exp. | Remote</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tms Llc</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Myrtle Point, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f9165e901d9215a</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Semantic Data Engineer | Digital Operations</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Beta Technologies</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>South Burlington, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d6de05e95a1a1c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Data Lake, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AWS Technical Apprentice / Trainee</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Pinecone, S3, Glue, Docker, Kubernetes, CI/CD, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176701077a642772</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Database Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Chess.com</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5a14d40ff745332</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Thinking Machines</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1489cd8bfd124930</t>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Mistral, PyTorch, Data Lake, Terraform, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f1dba196bac0927</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer, Security</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Thinking Machines</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Mistral, PyTorch, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a184a130661a3b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Engineer, Developer Productivity, AI Tools</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Thinking Machines</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Mistral, PyTorch, Docker, Kubernetes, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=952300d208ec7e6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Radiant Security</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Python, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=634af8f4d27319ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior SRE</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8e1794c0bb9b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior SRE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53e1260adba3967e</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Infrastructure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Upstart</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ohio, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89bb06907c547325</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Software Engineer - Sr Consultant level</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a391d284bead1fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Infrastructure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Upstart</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8299653e2a51a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RecruitIQ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Redshift, Databricks, Redshift, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22fdfae74b047784</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05813bd035198afe</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Software Engineer, AI Compute Infrastructure</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54e6a55634c338ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Backend Engineer - Infrastructure</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Kubernetes, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54b65be9c33e9ae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Veeam Software</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Redshift, Snowflake, Databricks, Redshift, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8ee797f8522e230</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Scientist, Digital Product Analytics</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GPS Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f21cb391b30035b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-04.xlsx
+++ b/daily_matches/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5f1f057c765d5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cala Health</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>25.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, Pinecone, S3, FastAPI, Docker, Terraform, PostgreSQL, MySQL</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc99bb2539da403</t>
+          <t>https://www.indeed.com/viewjob?jk=8af28ed89b784a62</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>25.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, FastAPI, Docker, CI/CD, Git, PySpark, PostgreSQL</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
+          <t>https://www.indeed.com/viewjob?jk=da31900dca44a1d5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3483120003abe</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Synapse, Data Lake, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9f9caf39a44baa</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI ML Engineer - Remote</t>
+          <t>Advanced Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7173b979af90a178</t>
+          <t>https://www.indeed.com/viewjob?jk=14533c5ea4cb3a4c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Docker, CI/CD, Terraform, Git, Redshift, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Kinesis, Terraform, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Basis Platform / DSP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, MongoDB, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a919fc520a45f74c</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer, Finance Data &amp; BI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, MLflow, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Community Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pulumi</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, PyTorch, Docker, Kubernetes, Python, R, Java</t>
+          <t>RAG, Glue, Athena, Kinesis, CI/CD, Git, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89f0037d93d86bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cae956ca669aed0b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FourKites</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, AKS, Git, Snowflake, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba292618629b2a9</t>
+          <t>https://www.indeed.com/viewjob?jk=89ee9ea3fd405574</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, AKS, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534286668d39390f</t>
+          <t>https://www.indeed.com/viewjob?jk=73d730532d5494d8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, Git, MySQL, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=e53834bd74a1ba40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Eden, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, Redshift, Docker, CI/CD, Redshift, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5647d0dbbaa33cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e126e60736d5dd15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Applied AI/ML Scientist</t>
+          <t>QA Engineer, AI &amp; Platform Infrastructure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NobleAI</t>
+          <t>ImmunityBio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Keras, Python, R, Scala, Optimization</t>
+          <t>LangChain, LLaMA, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2128d832986f1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=62997e81fdef97b1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Golang Software Engineer</t>
+          <t>Associate SDET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IDT Corporation</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kafka, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,1582 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a4850dc6cf9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=df4d7d392be99050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Digital / Data &amp; AI Engineer</t>
+          <t>Associate SDET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06709b3c1ff6780d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hudson, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0aadbade78d406e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Derby, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b113800489af906</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36f06e86821548bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7b3eab569ecb8a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=007e08599d2d0abb</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e12492a5258b3676</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Liberty, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f65671a3097ea26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c83c11fc10e081ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a08d0374a0e31c56</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f2b01bde7aa507b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Frankfort, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2e016cb3e91eb1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Barrington, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55394f4ba03e4923</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50c159b0a8e7da6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Newport, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2798704b652ffc40</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fargo, ND, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38ae2170954b9f0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4e5bd8f6bd72f1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=484235886733e39e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Richland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72b388a3058d07e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77e56d5d3396a6f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dayton, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ac4fb2ed6b0b47e</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e15521e8ddbca508</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8c73be21c65048d</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tyler, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e63b01d548cb8015</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97dc9487e8fdf03c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Medway, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ba5edaf476d5fc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bd05642d22da6f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Parlin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=869a46e5c095ad29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Stafford, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58107f0750003dbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Rehoboth Beach, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8968d299a3a43d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc7fc0734951160c</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Missoula, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e70a511828acefc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bb1e4109b667dfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3863a2787b67ac17</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Associate SDET</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Clinton, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82379dfc0a7484f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Daycos</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Norfolk, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08fac27d9fee4d7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Platform Infrastructure</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, Copilot, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=048aa873416bd1b1</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e38bc46ece036240</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer, Full Stack</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ImmunityBio</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LangChain, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0973d118144a57f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full-Stack, JavaScript)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Textron Aviation</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a90d350869dbc59</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cca15c735e4a8f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Credit Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf206404592cd871</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Solutions Specialist</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>E3 Consulting</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>San Juan, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=408440ad9dce735a</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Restaurant Depot</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Whitestone, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Apache Airflow, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82077ade18842d04</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Deerfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Git, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba0a90cfa43042c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Eden, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c546e262bd150502</t>
         </is>
       </c>
     </row>
